--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS01_cohort_description.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS01_cohort_description.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>One row per analysis (17 analyses over 16 region-level cohorts; the BrainSEQ schizophrenia caudate analysis includes the 238 control donors of the aging caudate analysis). Each donor contributes one sample per analysis. Age is in years; GTEx exact age is released top-coded at 70. BrainSEQ reports postmortem interval (PMI, h) and GTEx tissue ischemic time (min). Genes and transcripts are counts after the bundle expression filter, before the prevalence filter applied at module fitting. The CSV adds library kit, self-reported ancestry, manner of death or Hardy scale, feature counts before filtering and the snRNA-seq reference used for MuSiC deconvolution.</t>
+          <t>One row per analysis (17 analyses over 16 region-level cohorts; the BrainSEQ schizophrenia caudate analysis includes the 238 control donors of the aging caudate analysis). Each donor contributes one sample per analysis. Age is in years; Genotype-Tissue Expression (GTEx) exact age is released top-coded at 70. BrainSEQ reports postmortem interval (PMI, h) and GTEx tissue ischemic time (min). Genes and transcripts are counts after the bundle expression filter, before the prevalence filter applied at module fitting. The CSV adds library kit, self-reported ancestry, manner of death or Hardy scale, feature counts before filtering, and the single-nucleus RNA-sequencing (snRNA-seq) reference used for MuSiC deconvolution.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 by manuscript/_h/build_supplementary_data.py</t>
+          <t>2026-10-04 by manuscript/_h/build_supplementary_data.py</t>
         </is>
       </c>
     </row>
